--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-04-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-04-2025.xlsx
@@ -134,6 +134,411 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>£11.97</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>£12.29</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>£11.19</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>£11.98</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>£11.20</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>£13.74</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>£14.06</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>£12.79</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>£13.60</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>£13.78</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>£17.07</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>£17.59</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>£15.49</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>£18.03</t>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <t>£16.86</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>£17.85</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>£18.87</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>£16.89</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>£18.11</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>£17.33</t>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>£23.05</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>£23.87</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0" shapeId="0">
+      <text>
+        <t>£21.49</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>£23.04</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0">
+      <text>
+        <t>£21.37</t>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
+      <text>
+        <t>£25.36</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>£25.85</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>£22.99</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>£26.13</t>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0">
+      <text>
+        <t>£23.58</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <t>£25.40</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>£26.07</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>£23.49</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>£25.19</t>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0">
+      <text>
+        <t>£23.96</t>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <t>£28.81</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>£29.92</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>£26.99</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>£28.94</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
+      <text>
+        <t>£26.47</t>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0">
+      <text>
+        <t>£31.70</t>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0">
+      <text>
+        <t>£32.12</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>£28.99</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>£31.09</t>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0">
+      <text>
+        <t>£29.52</t>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0" shapeId="0">
+      <text>
+        <t>£29.99</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0">
+      <text>
+        <t>£31.89</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>£28.99</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>£31.06</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
+      <text>
+        <t>£30.30</t>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0">
+      <text>
+        <t>£40.01</t>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0">
+      <text>
+        <t>£41.69</t>
+      </text>
+    </comment>
+    <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <t>£37.99</t>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0">
+      <text>
+        <t>£38.29</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>£38.72</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>£34.99</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>£37.53</t>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0" shapeId="0">
+      <text>
+        <t>£35.40</t>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0">
+      <text>
+        <t>£45.66</t>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0">
+      <text>
+        <t>£46.70</t>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0">
+      <text>
+        <t>£42.49</t>
+      </text>
+    </comment>
+    <comment ref="L14" authorId="0" shapeId="0">
+      <text>
+        <t>£45.57</t>
+      </text>
+    </comment>
+    <comment ref="N14" authorId="0" shapeId="0">
+      <text>
+        <t>£35.40</t>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0" shapeId="0">
+      <text>
+        <t>£46.60</t>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0" shapeId="0">
+      <text>
+        <t>£48.95</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>£42.99</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>£46.10</t>
+      </text>
+    </comment>
+    <comment ref="N15" authorId="0" shapeId="0">
+      <text>
+        <t>£44.08</t>
+      </text>
+    </comment>
+    <comment ref="G16" authorId="0" shapeId="0">
+      <text>
+        <t>£46.94</t>
+      </text>
+    </comment>
+    <comment ref="H16" authorId="0" shapeId="0">
+      <text>
+        <t>£49.48</t>
+      </text>
+    </comment>
+    <comment ref="K16" authorId="0" shapeId="0">
+      <text>
+        <t>£44.99</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>£48.25</t>
+      </text>
+    </comment>
+    <comment ref="N16" authorId="0" shapeId="0">
+      <text>
+        <t>£43.99</t>
+      </text>
+    </comment>
+    <comment ref="K23" authorId="0" shapeId="0">
+      <text>
+        <t>£387.5</t>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0" shapeId="0">
+      <text>
+        <t>£505.25</t>
+      </text>
+    </comment>
+    <comment ref="K24" authorId="0" shapeId="0">
+      <text>
+        <t>£426.0</t>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0" shapeId="0">
+      <text>
+        <t>£500.45000000000005</t>
+      </text>
+    </comment>
+    <comment ref="K25" authorId="0" shapeId="0">
+      <text>
+        <t>£380.88</t>
+      </text>
+    </comment>
+    <comment ref="L25" authorId="0" shapeId="0">
+      <text>
+        <t>£507.12</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2855,5 +3260,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>